--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="429">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Generic treatment/rehabilitation profile for ICH, SAH, CVT, craniectomy, therapy, smoking cessation and shunt procedures not given a dedicated meta.profile in the Python builders.</t>
+    <t>Generic treatment and rehabilitation profile for ICH, SAH, CVT, craniectomy, therapy, smoking cessation and shunt procedures not given a dedicated meta.profile in the Python builders.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -710,7 +710,7 @@
 </t>
   </si>
   <si>
-    <t>Identification of the procedure</t>
+    <t>Treatment, rehabilitation or neurosurgical procedure</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -748,10 +748,10 @@
 </t>
   </si>
   <si>
-    <t>Individual or entity the procedure was performed on</t>
-  </si>
-  <si>
-    <t>On whom or on what the procedure was performed. This is usually an individual human, but can also be performed on animals, groups of humans or animals, organizations or practitioners (for licensing), locations or devices (for safety inspections or regulatory authorizations).  If the actual focus of the procedure is different from the subject, the focus element specifies the actual focus of the procedure.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -786,10 +786,10 @@
 </t>
   </si>
   <si>
-    <t>The Encounter during which this Procedure was created</t>
-  </si>
-  <si>
-    <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
@@ -814,7 +814,7 @@
 PeriodRange</t>
   </si>
   <si>
-    <t>When the procedure occurred or is occurring</t>
+    <t>Procedure date/time, interval or timing range</t>
   </si>
   <si>
     <t>Estimated or actual date, date-time, period, or age when the procedure did occur or is occurring.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
@@ -1104,7 +1104,7 @@
 </t>
   </si>
   <si>
-    <t>The justification that the procedure was performed</t>
+    <t>Clinical reason for treatment</t>
   </si>
   <si>
     <t>The coded reason or reference why the procedure was performed. This may be a coded entity of some type, be present as text, or be a reference to one of several resources that justify the procedure.</t>
@@ -1567,98 +1567,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1844,10 +1846,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1927,7 +1929,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1860" uniqueCount="428">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,10 +719,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>A code to identify a specific procedure .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code|5.0.0</t>
+    <t>http://tecnomod-um.org/ValueSet/ich-treatment-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -3947,13 +3944,11 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="Y20" s="2"/>
+      <c r="Z20" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3986,28 +3981,28 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>229</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4026,13 +4021,13 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4083,7 +4078,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>88</v>
@@ -4098,24 +4093,24 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AM21" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4138,13 +4133,13 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4195,7 +4190,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4213,7 +4208,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4224,10 +4219,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4250,16 +4245,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4309,7 +4304,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4324,24 +4319,24 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>251</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4364,16 +4359,16 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4423,7 +4418,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4438,24 +4433,24 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4478,13 +4473,13 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4535,7 +4530,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4550,13 +4545,13 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4564,10 +4559,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4590,13 +4585,13 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4647,7 +4642,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4665,10 +4660,10 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4676,14 +4671,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4702,17 +4697,17 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4761,7 +4756,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4776,13 +4771,13 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4790,10 +4785,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4816,13 +4811,13 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4873,7 +4868,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4885,16 +4880,16 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4902,10 +4897,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4928,13 +4923,13 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4985,7 +4980,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4994,19 +4989,19 @@
         <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5014,10 +5009,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5043,10 +5038,10 @@
         <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>151</v>
@@ -5099,7 +5094,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5120,7 +5115,7 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5128,14 +5123,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5157,10 +5152,10 @@
         <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>151</v>
@@ -5215,7 +5210,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5244,10 +5239,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5273,14 +5268,14 @@
         <v>202</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5308,11 +5303,11 @@
         <v>213</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>311</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5329,7 +5324,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5344,24 +5339,24 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>314</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5384,17 +5379,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5443,7 +5438,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>88</v>
@@ -5452,30 +5447,30 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>324</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5498,19 +5493,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>329</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5559,7 +5554,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5568,7 +5563,7 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>100</v>
@@ -5580,7 +5575,7 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5588,10 +5583,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5614,13 +5609,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5671,7 +5666,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5700,10 +5695,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5726,13 +5721,13 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5783,7 +5778,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5801,21 +5796,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5838,16 +5833,16 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5876,11 +5871,11 @@
         <v>213</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5897,7 +5892,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5912,24 +5907,24 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5955,13 +5950,13 @@
         <v>202</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5990,11 +5985,11 @@
         <v>213</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6011,7 +6006,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6032,18 +6027,18 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6069,13 +6064,13 @@
         <v>202</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6104,11 +6099,11 @@
         <v>213</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6125,7 +6120,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6146,7 +6141,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6154,10 +6149,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6180,16 +6175,16 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6239,7 +6234,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6260,7 +6255,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6268,10 +6263,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6294,16 +6289,16 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6332,11 +6327,11 @@
         <v>213</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>381</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6353,7 +6348,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6374,7 +6369,7 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -6382,10 +6377,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6411,10 +6406,10 @@
         <v>202</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6444,11 +6439,11 @@
         <v>213</v>
       </c>
       <c r="Y42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z42" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="Z42" t="s" s="2">
-        <v>387</v>
-      </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6465,7 +6460,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6486,7 +6481,7 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6494,10 +6489,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6520,13 +6515,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6577,7 +6572,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6592,24 +6587,24 @@
         <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6632,13 +6627,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6689,7 +6684,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6710,7 +6705,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6718,10 +6713,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6744,13 +6739,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6801,7 +6796,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6810,19 +6805,19 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6830,10 +6825,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6859,10 +6854,10 @@
         <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>151</v>
@@ -6915,7 +6910,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6936,7 +6931,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6944,14 +6939,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6973,10 +6968,10 @@
         <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>151</v>
@@ -7031,7 +7026,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7060,10 +7055,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7089,10 +7084,10 @@
         <v>202</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7119,14 +7114,14 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7143,7 +7138,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7164,7 +7159,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7172,10 +7167,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7198,13 +7193,13 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7255,7 +7250,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>88</v>
@@ -7276,7 +7271,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7284,10 +7279,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7310,19 +7305,19 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7350,11 +7345,11 @@
         <v>213</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>422</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7371,7 +7366,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7392,7 +7387,7 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7400,10 +7395,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7426,13 +7421,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7483,7 +7478,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7504,7 +7499,7 @@
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,7 +719,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/ich-treatment-vs</t>
+    <t>http://tecnomod-um.org/ValueSet/post-stroke-procedures-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -3944,7 +3944,7 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>206</v>
+        <v>112</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -719,7 +719,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/post-stroke-procedures-vs</t>
+    <t>http://tecnomod-um.org/ValueSet/stroke-treatment-procedure-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1703,7 +1703,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.79296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.21875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -3944,7 +3944,7 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/stroke-treatment-procedure-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/stroke-treatment-procedure-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -466,7 +466,7 @@
     <t>procedureTimingContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://tecnomod-um.org/StructureDefinition/procedure-timing-context-ext}
+    <t xml:space="preserve">Extension {http://qualityregistry.org/StructureDefinition/procedure-timing-context-ext}
 </t>
   </si>
   <si>
@@ -667,7 +667,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/procedure-not-done-reason-vs</t>
+    <t>http://qualityregistry.org/ValueSet/procedure-not-done-reason-vs</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -719,7 +719,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/stroke-treatment-procedure-vs</t>
+    <t>http://qualityregistry.org/ValueSet/stroke-treatment-procedure-vs</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -741,7 +741,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -779,7 +779,7 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>
@@ -1703,7 +1703,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="62.6328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.21875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.6640625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-treatment-procedure-profile.xlsx
+++ b/StructureDefinition-stroke-treatment-procedure-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
